--- a/data/trans_orig/IP16A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21934</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>13529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24301</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20140</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26517</t>
+          <t>26734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25538</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36916</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26108</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39559</t>
+          <t>39076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>32766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47371</t>
+          <t>46600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47721</t>
+          <t>47760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66525</t>
+          <t>66810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83353</t>
+          <t>81515</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108287</t>
+          <t>106643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62363</t>
+          <t>63134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78799</t>
+          <t>78420</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68772</t>
+          <t>68487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87576</t>
+          <t>87537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136743</t>
+          <t>138387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>161677</t>
+          <t>163515</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>20877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>39266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,87%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11893</t>
+          <t>11863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15495</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29291</t>
+          <t>29472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33606</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58808</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43457</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39147</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53058</t>
+          <t>53035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74423</t>
+          <t>73733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93868</t>
+          <t>92610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>39733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>46845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68098</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89431</t>
+          <t>88573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61257</t>
+          <t>62097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83114</t>
+          <t>83211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135295</t>
+          <t>135082</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166840</t>
+          <t>167204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89468</t>
+          <t>90326</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110801</t>
+          <t>111893</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97054</t>
+          <t>96957</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118911</t>
+          <t>118071</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>192227</t>
+          <t>191863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>223772</t>
+          <t>223985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33604</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28850</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,22%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>46071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26505</t>
+          <t>27056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23089</t>
+          <t>23081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>32938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54118</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68898</t>
+          <t>69161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,9%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>34668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47584</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21198</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70347</t>
+          <t>70321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42541</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60887</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98233</t>
+          <t>98371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124305</t>
+          <t>126513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86753</t>
+          <t>86779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106630</t>
+          <t>106163</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78767</t>
+          <t>78385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>97113</t>
+          <t>97994</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>172450</t>
+          <t>170242</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>198522</t>
+          <t>198384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39063</t>
+          <t>40327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27968</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>19690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>37904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61732</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37635</t>
+          <t>38477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68267</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70493</t>
+          <t>72250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>110010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>19319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35081</t>
+          <t>34451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>43814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46224</t>
+          <t>39191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89179</t>
+          <t>90404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66964</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91262</t>
+          <t>91023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115533</t>
+          <t>114118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173068</t>
+          <t>172392</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86208</t>
+          <t>84983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>136196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>88286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112345</t>
+          <t>111116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>181629</t>
+          <t>182305</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>239164</t>
+          <t>240579</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
